--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasdambreville/Dev/Perso/wallet_simplify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA690D6-6EC4-9344-9A46-90AEAA42B325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5455582F-4F41-5B42-A1B5-922C97944A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,7 +171,7 @@
     <t>3) la table transaction permet de noter tous les achats et les ventes réalisées</t>
   </si>
   <si>
-    <t>priceprice/unit</t>
+    <t>price_unit</t>
   </si>
 </sst>
 </file>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,24 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasdambreville/Dev/Perso/wallet_simplify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5455582F-4F41-5B42-A1B5-922C97944A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1BDF54-AB9A-E246-8B09-7891A43CF1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Assets" sheetId="3" r:id="rId2"/>
     <sheet name="Transactions" sheetId="4" r:id="rId3"/>
     <sheet name="Settings" sheetId="2" r:id="rId4"/>
-    <sheet name="Prices" sheetId="5" r:id="rId5"/>
-    <sheet name="FX" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
   <si>
     <t>MyWallet (Excel) — Template</t>
   </si>
@@ -108,18 +106,12 @@
     <t>Amundi MSCI World (ex)</t>
   </si>
   <si>
-    <t>Euronext Paris</t>
-  </si>
-  <si>
     <t>AAPL</t>
   </si>
   <si>
     <t>Apple</t>
   </si>
   <si>
-    <t>NASDAQ</t>
-  </si>
-  <si>
     <t>BTC</t>
   </si>
   <si>
@@ -129,9 +121,6 @@
     <t>Euro cash</t>
   </si>
   <si>
-    <t>Cash position</t>
-  </si>
-  <si>
     <t>date</t>
   </si>
   <si>
@@ -141,9 +130,6 @@
     <t>quantity</t>
   </si>
   <si>
-    <t>price</t>
-  </si>
-  <si>
     <t>note</t>
   </si>
   <si>
@@ -153,15 +139,6 @@
     <t>2026-01-15</t>
   </si>
   <si>
-    <t>pair</t>
-  </si>
-  <si>
-    <t>rate</t>
-  </si>
-  <si>
-    <t>USD_EUR</t>
-  </si>
-  <si>
     <t>1) Modifier UNIQUEMENT les tables Transactions et Assets</t>
   </si>
   <si>
@@ -172,6 +149,9 @@
   </si>
   <si>
     <t>price_unit</t>
+  </si>
+  <si>
+    <t>Bank</t>
   </si>
 </sst>
 </file>
@@ -213,7 +193,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -236,11 +216,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -249,18 +242,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -579,17 +568,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -599,16 +588,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
@@ -622,10 +612,13 @@
         <v>23</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -638,16 +631,14 @@
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -655,16 +646,14 @@
       <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
@@ -672,16 +661,14 @@
       <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -689,9 +676,7 @@
       <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="E5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -725,34 +710,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>4</v>
@@ -776,13 +761,13 @@
     </row>
     <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
@@ -1054,153 +1039,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="5" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="3">
-        <v>420.5</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="3">
-        <v>423.1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="3">
-        <v>195.2</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{00000000-000E-0000-0400-000001000000}">
-            <xm:f>AND($B2&lt;&gt;"",COUNTIF(Assets!$A:$A,$B2)=0)</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:B20000</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0400-000000000000}">
-          <x14:formula1>
-            <xm:f>Assets!$A$2:$A$1000</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B20000</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
-          <x14:formula1>
-            <xm:f>Settings!$C$2:$C$20</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D20000</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="4" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.92</v>
-      </c>
-      <c r="D2" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>